--- a/data/taches.xlsx
+++ b/data/taches.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sschies1\_code\1.09_VScode\06_VoeuxConcerts\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4704CDF9-0CDF-41D4-93A2-FDDECE0A0144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6C082FC-1FF0-4A5E-8F1A-42D684DC29BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{1E9D0330-7709-483D-BFE5-B7F0B42F0045}"/>
   </bookViews>
@@ -39,33 +39,27 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>Tâche</t>
   </si>
   <si>
-    <t>Ailes</t>
-  </si>
-  <si>
-    <t>Bar public</t>
-  </si>
-  <si>
-    <t>Bar loges</t>
-  </si>
-  <si>
-    <t>Entrée</t>
-  </si>
-  <si>
-    <t>Tech PCGB</t>
-  </si>
-  <si>
-    <t>Tech Terriens</t>
-  </si>
-  <si>
-    <t>Tech Jacquard</t>
-  </si>
-  <si>
-    <t>Tech Muchmuche</t>
+    <t>Vestiaire</t>
+  </si>
+  <si>
+    <t>Technique</t>
+  </si>
+  <si>
+    <t>Bar</t>
+  </si>
+  <si>
+    <t>Sécurité</t>
+  </si>
+  <si>
+    <t>Accueil</t>
+  </si>
+  <si>
+    <t>Billetterie</t>
   </si>
 </sst>
 </file>
@@ -446,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0924BC-588A-4AAE-BEAF-79BB8BC4D313}">
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="18.4609375" customWidth="1"/>
@@ -459,17 +453,17 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.4">
@@ -479,22 +473,12 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
